--- a/excel2template/test/RDEDatasetTemplateSheet_test_02.xlsx
+++ b/excel2template/test/RDEDatasetTemplateSheet_test_02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nims_tosaka/Documents/RDE/gitlab/common-materials/rde_template_tools/excel2template/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDB70F3-57F1-E047-BDA4-D3B8F0F1C31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8434F7-A379-C446-BAD9-B6247722D4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39020" yWindow="600" windowWidth="31340" windowHeight="21040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2000" yWindow="1580" windowWidth="31340" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="説明" sheetId="13" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2609" uniqueCount="1515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2609" uniqueCount="1516">
   <si>
     <t>category</t>
     <phoneticPr fontId="2"/>
@@ -5219,13 +5219,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Aa123文字列</t>
-    <rPh sb="5" eb="8">
-      <t xml:space="preserve">モジレツ </t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>my_textarea</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -5312,6 +5305,20 @@
   </si>
   <si>
     <t>RDEDatasetTemplateSheet_test_02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Aa123文字列,xyz987文字列2</t>
+    <rPh sb="5" eb="8">
+      <t xml:space="preserve">モジレツ </t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t xml:space="preserve">レツ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>tiff,jpeg</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -5747,6 +5754,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -5765,9 +5784,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -5776,15 +5792,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5820,14 +5827,7 @@
     <cellStyle name="標準 2" xfId="1" xr:uid="{40251804-E9E9-43A3-956E-E079063D14C4}"/>
     <cellStyle name="標準 4" xfId="2" xr:uid="{965AAE8D-7E1A-4798-B53C-4043C6350A54}"/>
   </cellStyles>
-  <dxfs count="31">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="30">
     <dxf>
       <fill>
         <patternFill>
@@ -6500,7 +6500,7 @@
         <v>1383</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C1" s="31" t="s">
         <v>1384</v>
@@ -6511,7 +6511,7 @@
         <v>1385</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C2" s="31" t="s">
         <v>1384</v>
@@ -6522,7 +6522,7 @@
         <v>1386</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C3" s="31" t="s">
         <v>1387</v>
@@ -6545,7 +6545,7 @@
         <v>1389</v>
       </c>
       <c r="B6" s="39">
-        <v>46125</v>
+        <v>46155</v>
       </c>
       <c r="C6" s="31"/>
     </row>
@@ -6563,7 +6563,7 @@
         <v>1391</v>
       </c>
       <c r="B8" s="39">
-        <v>46125</v>
+        <v>46155</v>
       </c>
       <c r="C8" s="31"/>
     </row>
@@ -6694,20 +6694,20 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="B1:B3">
-    <cfRule type="expression" dxfId="30" priority="3">
+    <cfRule type="expression" dxfId="29" priority="3">
       <formula>"ISBLANK(B3)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B3">
-    <cfRule type="expression" dxfId="29" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="1" stopIfTrue="1">
       <formula>ISBLANK(B2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="4" stopIfTrue="1">
       <formula>ISBLANK(B2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="expression" dxfId="27" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="7" stopIfTrue="1">
       <formula>ISBLANK(B1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8191,15 +8191,15 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"OFF"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
       <formula>"ON"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576 G1:H1048576 J1:J1048576">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>AND($B1="ON",ISBLANK(C1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8261,12 +8261,12 @@
       <c r="A1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="59"/>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
       <c r="H1" s="18"/>
@@ -8287,13 +8287,13 @@
       <c r="A2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="60" t="str">
+      <c r="B2" s="63" t="str">
         <f>"https://rde.nims.go.jp/rde/dataset-templates/"&amp;説明!B3&amp;"/invoice.schema.json"</f>
         <v>https://rde.nims.go.jp/rde/dataset-templates/RDEDatasetTemplateSheet_test_02/invoice.schema.json</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="62"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
       <c r="H2" s="18"/>
@@ -8314,13 +8314,13 @@
       <c r="A3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="56" t="str">
+      <c r="B3" s="60" t="str">
         <f>説明!B4&amp;": 送状定義"</f>
         <v>送状定義/固有情報の項目あり、試料情報なし: 送状定義</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="58"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="62"/>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
       <c r="H3" s="18"/>
@@ -8538,10 +8538,10 @@
       </c>
     </row>
     <row r="7" spans="1:29">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="53" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -8588,10 +8588,10 @@
       <c r="S7" s="19"/>
       <c r="T7" s="19"/>
       <c r="U7" s="19" t="s">
+        <v>1510</v>
+      </c>
+      <c r="V7" s="19" t="s">
         <v>1511</v>
-      </c>
-      <c r="V7" s="19" t="s">
-        <v>1512</v>
       </c>
       <c r="W7" s="19"/>
       <c r="X7" s="19"/>
@@ -8602,8 +8602,8 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="1:29">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="53"/>
       <c r="C8" s="4" t="s">
         <v>1402</v>
       </c>
@@ -8660,8 +8660,8 @@
       <c r="AC8" s="19"/>
     </row>
     <row r="9" spans="1:29">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="4" t="s">
         <v>1402</v>
       </c>
@@ -8718,8 +8718,8 @@
       <c r="AC9" s="19"/>
     </row>
     <row r="10" spans="1:29">
-      <c r="A10" s="59"/>
-      <c r="B10" s="59"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="53"/>
       <c r="C10" s="4" t="s">
         <v>1402</v>
       </c>
@@ -8737,7 +8737,7 @@
         <v>1498</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>1499</v>
+        <v>1514</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="23"/>
@@ -8774,26 +8774,26 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="1:29">
-      <c r="A11" s="59"/>
-      <c r="B11" s="59"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="53"/>
       <c r="C11" s="4" t="s">
         <v>1402</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="E11" s="28"/>
       <c r="F11" s="22" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>1499</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>1500</v>
+      </c>
+      <c r="I11" s="19" t="s">
         <v>1501</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>1500</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>1501</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>1502</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="23"/>
@@ -8830,32 +8830,32 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="1:29">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="53"/>
       <c r="C12" s="4" t="s">
         <v>1402</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="E12" s="28"/>
       <c r="F12" s="22" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>1502</v>
+      </c>
+      <c r="H12" s="19" t="s">
         <v>1504</v>
       </c>
-      <c r="G12" s="22" t="s">
-        <v>1503</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>1505</v>
-      </c>
       <c r="I12" s="19" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="J12" s="19"/>
       <c r="K12" s="23"/>
       <c r="L12" s="8"/>
       <c r="M12" s="7" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="N12" s="38" t="str">
         <f t="shared" si="0"/>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="Q12" s="28"/>
       <c r="R12" s="28" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="S12" s="19"/>
       <c r="T12" s="19"/>
@@ -8886,23 +8886,23 @@
       <c r="AC12" s="19"/>
     </row>
     <row r="13" spans="1:29">
-      <c r="A13" s="59"/>
-      <c r="B13" s="59"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="53"/>
       <c r="C13" s="4" t="s">
         <v>1402</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="E13" s="28"/>
       <c r="F13" s="22" t="s">
+        <v>1508</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>1507</v>
+      </c>
+      <c r="H13" s="19" t="s">
         <v>1509</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>1508</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>1510</v>
       </c>
       <c r="I13" s="19" t="b">
         <v>1</v>
@@ -8940,8 +8940,8 @@
       <c r="AC13" s="19"/>
     </row>
     <row r="14" spans="1:29">
-      <c r="A14" s="59"/>
-      <c r="B14" s="59"/>
+      <c r="A14" s="53"/>
+      <c r="B14" s="53"/>
       <c r="C14" s="4" t="s">
         <v>44</v>
       </c>
@@ -8984,8 +8984,8 @@
       <c r="AC14" s="1"/>
     </row>
     <row r="15" spans="1:29">
-      <c r="A15" s="59"/>
-      <c r="B15" s="59"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="4" t="s">
         <v>44</v>
       </c>
@@ -9028,8 +9028,8 @@
       <c r="AC15" s="1"/>
     </row>
     <row r="16" spans="1:29">
-      <c r="A16" s="59"/>
-      <c r="B16" s="59"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="53"/>
       <c r="C16" s="4" t="s">
         <v>44</v>
       </c>
@@ -9072,8 +9072,8 @@
       <c r="AC16" s="1"/>
     </row>
     <row r="17" spans="1:29">
-      <c r="A17" s="59"/>
-      <c r="B17" s="59"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="53"/>
       <c r="C17" s="4" t="s">
         <v>44</v>
       </c>
@@ -9116,10 +9116,10 @@
       <c r="AC17" s="1"/>
     </row>
     <row r="18" spans="1:29">
-      <c r="A18" s="63" t="s">
+      <c r="A18" s="54" t="s">
         <v>1379</v>
       </c>
-      <c r="B18" s="59" t="s">
+      <c r="B18" s="53" t="s">
         <v>79</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -9159,8 +9159,8 @@
       <c r="AC18" s="28"/>
     </row>
     <row r="19" spans="1:29">
-      <c r="A19" s="64"/>
-      <c r="B19" s="59"/>
+      <c r="A19" s="55"/>
+      <c r="B19" s="53"/>
       <c r="C19" s="4" t="s">
         <v>44</v>
       </c>
@@ -9198,8 +9198,8 @@
       <c r="AC19" s="28"/>
     </row>
     <row r="20" spans="1:29">
-      <c r="A20" s="64"/>
-      <c r="B20" s="59"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="53"/>
       <c r="C20" s="4" t="s">
         <v>44</v>
       </c>
@@ -9237,8 +9237,8 @@
       <c r="AC20" s="28"/>
     </row>
     <row r="21" spans="1:29">
-      <c r="A21" s="64"/>
-      <c r="B21" s="59"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="53"/>
       <c r="C21" s="4" t="s">
         <v>44</v>
       </c>
@@ -9276,8 +9276,8 @@
       <c r="AC21" s="28"/>
     </row>
     <row r="22" spans="1:29">
-      <c r="A22" s="64"/>
-      <c r="B22" s="59"/>
+      <c r="A22" s="55"/>
+      <c r="B22" s="53"/>
       <c r="C22" s="4" t="s">
         <v>44</v>
       </c>
@@ -9315,8 +9315,8 @@
       <c r="AC22" s="28"/>
     </row>
     <row r="23" spans="1:29">
-      <c r="A23" s="64"/>
-      <c r="B23" s="59"/>
+      <c r="A23" s="55"/>
+      <c r="B23" s="53"/>
       <c r="C23" s="4" t="s">
         <v>44</v>
       </c>
@@ -9354,8 +9354,8 @@
       <c r="AC23" s="28"/>
     </row>
     <row r="24" spans="1:29">
-      <c r="A24" s="65"/>
-      <c r="B24" s="59"/>
+      <c r="A24" s="56"/>
+      <c r="B24" s="53"/>
       <c r="C24" s="4" t="s">
         <v>44</v>
       </c>
@@ -9393,10 +9393,10 @@
       <c r="AC24" s="28"/>
     </row>
     <row r="25" spans="1:29">
-      <c r="A25" s="63" t="s">
+      <c r="A25" s="54" t="s">
         <v>1380</v>
       </c>
-      <c r="B25" s="59" t="s">
+      <c r="B25" s="53" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -9445,8 +9445,8 @@
       <c r="AC25" s="28"/>
     </row>
     <row r="26" spans="1:29">
-      <c r="A26" s="64"/>
-      <c r="B26" s="59"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="53"/>
       <c r="C26" s="4" t="s">
         <v>44</v>
       </c>
@@ -9493,8 +9493,8 @@
       <c r="AC26" s="28"/>
     </row>
     <row r="27" spans="1:29">
-      <c r="A27" s="64"/>
-      <c r="B27" s="59"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="53"/>
       <c r="C27" s="4" t="s">
         <v>44</v>
       </c>
@@ -9541,8 +9541,8 @@
       <c r="AC27" s="28"/>
     </row>
     <row r="28" spans="1:29">
-      <c r="A28" s="64"/>
-      <c r="B28" s="59"/>
+      <c r="A28" s="55"/>
+      <c r="B28" s="53"/>
       <c r="C28" s="4" t="s">
         <v>44</v>
       </c>
@@ -9589,8 +9589,8 @@
       <c r="AC28" s="28"/>
     </row>
     <row r="29" spans="1:29">
-      <c r="A29" s="64"/>
-      <c r="B29" s="59"/>
+      <c r="A29" s="55"/>
+      <c r="B29" s="53"/>
       <c r="C29" s="4" t="s">
         <v>44</v>
       </c>
@@ -9637,8 +9637,8 @@
       <c r="AC29" s="28"/>
     </row>
     <row r="30" spans="1:29">
-      <c r="A30" s="64"/>
-      <c r="B30" s="59"/>
+      <c r="A30" s="55"/>
+      <c r="B30" s="53"/>
       <c r="C30" s="4" t="s">
         <v>44</v>
       </c>
@@ -9685,8 +9685,8 @@
       <c r="AC30" s="28"/>
     </row>
     <row r="31" spans="1:29">
-      <c r="A31" s="64"/>
-      <c r="B31" s="59"/>
+      <c r="A31" s="55"/>
+      <c r="B31" s="53"/>
       <c r="C31" s="4" t="s">
         <v>44</v>
       </c>
@@ -9733,8 +9733,8 @@
       <c r="AC31" s="28"/>
     </row>
     <row r="32" spans="1:29">
-      <c r="A32" s="64"/>
-      <c r="B32" s="59"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="53"/>
       <c r="C32" s="4" t="s">
         <v>44</v>
       </c>
@@ -9781,8 +9781,8 @@
       <c r="AC32" s="28"/>
     </row>
     <row r="33" spans="1:29">
-      <c r="A33" s="65"/>
-      <c r="B33" s="59"/>
+      <c r="A33" s="56"/>
+      <c r="B33" s="53"/>
       <c r="C33" s="4" t="s">
         <v>44</v>
       </c>
@@ -9829,10 +9829,10 @@
       <c r="AC33" s="28"/>
     </row>
     <row r="34" spans="1:29">
-      <c r="A34" s="63" t="s">
+      <c r="A34" s="54" t="s">
         <v>1381</v>
       </c>
-      <c r="B34" s="59" t="s">
+      <c r="B34" s="53" t="s">
         <v>41</v>
       </c>
       <c r="C34" s="4" t="s">
@@ -9881,8 +9881,8 @@
       <c r="AC34" s="28"/>
     </row>
     <row r="35" spans="1:29">
-      <c r="A35" s="64"/>
-      <c r="B35" s="59"/>
+      <c r="A35" s="55"/>
+      <c r="B35" s="53"/>
       <c r="C35" s="4" t="s">
         <v>44</v>
       </c>
@@ -9929,8 +9929,8 @@
       <c r="AC35" s="28"/>
     </row>
     <row r="36" spans="1:29">
-      <c r="A36" s="64"/>
-      <c r="B36" s="59"/>
+      <c r="A36" s="55"/>
+      <c r="B36" s="53"/>
       <c r="C36" s="4" t="s">
         <v>44</v>
       </c>
@@ -9977,8 +9977,8 @@
       <c r="AC36" s="28"/>
     </row>
     <row r="37" spans="1:29">
-      <c r="A37" s="64"/>
-      <c r="B37" s="59"/>
+      <c r="A37" s="55"/>
+      <c r="B37" s="53"/>
       <c r="C37" s="4" t="s">
         <v>44</v>
       </c>
@@ -10025,8 +10025,8 @@
       <c r="AC37" s="28"/>
     </row>
     <row r="38" spans="1:29">
-      <c r="A38" s="64"/>
-      <c r="B38" s="59"/>
+      <c r="A38" s="55"/>
+      <c r="B38" s="53"/>
       <c r="C38" s="4" t="s">
         <v>44</v>
       </c>
@@ -10073,8 +10073,8 @@
       <c r="AC38" s="28"/>
     </row>
     <row r="39" spans="1:29">
-      <c r="A39" s="64"/>
-      <c r="B39" s="59"/>
+      <c r="A39" s="55"/>
+      <c r="B39" s="53"/>
       <c r="C39" s="4" t="s">
         <v>44</v>
       </c>
@@ -10121,8 +10121,8 @@
       <c r="AC39" s="28"/>
     </row>
     <row r="40" spans="1:29">
-      <c r="A40" s="64"/>
-      <c r="B40" s="59"/>
+      <c r="A40" s="55"/>
+      <c r="B40" s="53"/>
       <c r="C40" s="4" t="s">
         <v>44</v>
       </c>
@@ -10169,8 +10169,8 @@
       <c r="AC40" s="28"/>
     </row>
     <row r="41" spans="1:29">
-      <c r="A41" s="64"/>
-      <c r="B41" s="59"/>
+      <c r="A41" s="55"/>
+      <c r="B41" s="53"/>
       <c r="C41" s="4" t="s">
         <v>44</v>
       </c>
@@ -10217,8 +10217,8 @@
       <c r="AC41" s="28"/>
     </row>
     <row r="42" spans="1:29">
-      <c r="A42" s="65"/>
-      <c r="B42" s="59"/>
+      <c r="A42" s="56"/>
+      <c r="B42" s="53"/>
       <c r="C42" s="4" t="s">
         <v>44</v>
       </c>
@@ -10266,77 +10266,72 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B34:B42"/>
-    <mergeCell ref="B7:B17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A33"/>
-    <mergeCell ref="A34:A42"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A7:A17"/>
     <mergeCell ref="B25:B33"/>
     <mergeCell ref="B18:B24"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B34:B42"/>
+    <mergeCell ref="B7:B17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A33"/>
+    <mergeCell ref="A34:A42"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="B1:E1">
-    <cfRule type="expression" dxfId="23" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="2" stopIfTrue="1">
       <formula>ISBLANK(B1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C42">
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="20" operator="equal">
       <formula>"OFF"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="21" operator="equal">
       <formula>"ON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D24">
-    <cfRule type="expression" dxfId="20" priority="4">
-      <formula>AND($C18="ON",ISBLANK(D18))</formula>
+  <conditionalFormatting sqref="D7:D24">
+    <cfRule type="expression" dxfId="19" priority="1">
+      <formula>AND($C7="ON",ISBLANK(D7))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:G24">
-    <cfRule type="expression" dxfId="19" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>AND($C7="ON",ISBLANK(F7))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:M17 E25:E42">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="17" priority="18">
       <formula>AND($C7="ON",ISBLANK(E7))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7:O17">
-    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
       <formula>"ON"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q7:Q17">
-    <cfRule type="expression" dxfId="16" priority="5">
+    <cfRule type="expression" dxfId="15" priority="5">
       <formula>AND($C7="ON",$M7&lt;&gt;"textarea")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="7">
+    <cfRule type="expression" dxfId="14" priority="7">
       <formula>AND($C7="ON",$M7="textarea",ISBLANK($Q7))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="9">
+    <cfRule type="expression" dxfId="13" priority="9">
       <formula>AND($C7="ON",$M7="textarea")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R7:R17">
-    <cfRule type="expression" dxfId="13" priority="6">
+    <cfRule type="expression" dxfId="12" priority="6">
       <formula>AND($C7="ON",$M7&lt;&gt;"list")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8">
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>AND($C7="ON",$M7="list",ISBLANK($R7))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>AND($C7="ON",$M7="list")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D17">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND($C7="ON",ISBLANK(D7))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -10989,7 +10984,7 @@
       <c r="L13" s="28"/>
       <c r="M13" s="19"/>
       <c r="N13" s="19" t="s">
-        <v>1415</v>
+        <v>1515</v>
       </c>
       <c r="O13" s="19"/>
       <c r="P13" s="19"/>
@@ -11262,42 +11257,42 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="10" priority="9">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>ISBLANK(B1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="9" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
       <formula>"OFF"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="15" operator="equal">
       <formula>"ON"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:E1048576 G1:G1048576">
-    <cfRule type="expression" dxfId="7" priority="10">
+    <cfRule type="expression" dxfId="6" priority="10">
       <formula>AND($B1="ON",ISBLANK(C1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:K1048576">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>AND($B1="ON",$G1&lt;&gt;"textarea")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>AND($B1="ON",$G1="textarea",ISBLANK($K1))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="18">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>AND($B1="ON",$G1="textarea")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>AND($B1="ON",$G1&lt;&gt;"list")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>AND($B1="ON",$G1="list",ISBLANK($L1))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="19">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>AND($B1="ON",$G1="list")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21372,6 +21367,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="03d23630-19bc-4208-bade-29ad47d0e872" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fcac4235-3712-4f1a-9a68-cd81b1c94fd2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010051C3DC589983724E98472DFCE83CFE28" ma:contentTypeVersion="8" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="56ec90460d2d98ba0f9df34f0ad90fe5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fcac4235-3712-4f1a-9a68-cd81b1c94fd2" xmlns:ns3="03d23630-19bc-4208-bade-29ad47d0e872" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="64cd019f2d5f0eccec25873ecd453d84" ns2:_="" ns3:_="">
     <xsd:import namespace="fcac4235-3712-4f1a-9a68-cd81b1c94fd2"/>
@@ -21548,17 +21554,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="03d23630-19bc-4208-bade-29ad47d0e872" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fcac4235-3712-4f1a-9a68-cd81b1c94fd2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -21569,6 +21564,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB043C42-5D59-4A30-92A0-5EA74B604AF5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="03d23630-19bc-4208-bade-29ad47d0e872"/>
+    <ds:schemaRef ds:uri="fcac4235-3712-4f1a-9a68-cd81b1c94fd2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBBD398B-EE48-4CBF-8E35-C1D89BC3BAE8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21587,17 +21593,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB043C42-5D59-4A30-92A0-5EA74B604AF5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="03d23630-19bc-4208-bade-29ad47d0e872"/>
-    <ds:schemaRef ds:uri="fcac4235-3712-4f1a-9a68-cd81b1c94fd2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F1080EF-91B6-417D-A249-69224D257C51}">
   <ds:schemaRefs>
